--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_vol/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_vol/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -466,12 +466,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1742436531127713</v>
+        <v>0.2168324476824059</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2883229936159422</v>
+        <v>0.168121829810835</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.7217826725452731</v>
+        <v>1.31475426789817</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1.057899290492011</v>
+        <v>1.988792599527577</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2057339813645478</v>
+        <v>0.09086898773639007</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.9674125641663348</v>
+        <v>2.732367336564214</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>63.9832287874563</v>
+        <v>29.24162652471045</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.3147171300352747</v>
+        <v>0.1654637761461595</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2610378055778777</v>
+        <v>0.2849855015774532</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.433111788414852</v>
+        <v>0.6488334320591894</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.880752795507286</v>
+        <v>0.99552485223761</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3550988928403116</v>
+        <v>0.1621525093764552</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9161837655835801</v>
+        <v>1.066041585765974</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>60.92713701203446</v>
+        <v>46.61227457406678</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.01872008512625523</v>
+        <v>0.1761116914347538</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2268500150913955</v>
+        <v>0.2353137027351377</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.1325150564645733</v>
+        <v>0.7721309887636136</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1933470998222941</v>
+        <v>1.119756850064668</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2168080682991826</v>
+        <v>0.1723104996135127</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.08994654832216881</v>
+        <v>1.0679657295645</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>67.87707698613649</v>
+        <v>65.4527760009219</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.006409689836916255</v>
+        <v>0.4364175484056294</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2505614794008397</v>
+        <v>0.3590017633299322</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.03810290324780041</v>
+        <v>1.187683228756663</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.05693689396241713</v>
+        <v>1.840078958167369</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2459900626440827</v>
+        <v>0.165241451933674</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.0271298248537757</v>
+        <v>2.772156335821542</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>73.52444800101473</v>
+        <v>72.94355805738556</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.1668322794566566</v>
+        <v>0.3200454974918774</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2259744047038349</v>
+        <v>0.2566524069273824</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.7552780557070513</v>
+        <v>1.19325172953265</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.067922582743029</v>
+        <v>1.700457601424564</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1528989728210315</v>
+        <v>0.2022304821037131</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.134862296618343</v>
+        <v>1.650051948335714</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>74.24684004457305</v>
+        <v>77.66921658108927</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.3366107954068722</v>
+        <v>0.683783963768219</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.2903212016317365</v>
+        <v>0.3787873708320117</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.906474594615277</v>
+        <v>2.646251507984601</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.940407030316357</v>
+        <v>4.382750435552415</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1296377592784064</v>
+        <v>0.1257720586191925</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.339162019563085</v>
+        <v>12.49761625227006</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>60.64686116707578</v>
+        <v>53.70152832632016</v>
       </c>
     </row>
   </sheetData>
